--- a/reports/集团总公司_现金流量表_2026-10.xlsx
+++ b/reports/集团总公司_现金流量表_2026-10.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>210892500</v>
+        <v>206189009</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>2010845928</v>
+        <v>1975752693</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4230508</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>40750500</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2095412</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>20352816</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1056128</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>10192300</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>840069</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>8138715</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>631871</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>6116006</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>421365</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4069776</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>314946</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3057097</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>211267</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2035825</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>523790</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>5092232</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>265771</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2559442</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>166495</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1618065</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>573195</v>
+        <v>565170</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>5546344</v>
+        <v>5449878</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3893400</v>
+        <v>3815259</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>37673280</v>
+        <v>36999071</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>215359095</v>
+        <v>221327060</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>129780000</v>
+        <v>127057365</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1255776000</v>
+        <v>1234833692</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1409925</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>13577793</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1047155</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>10180165</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>704905</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>6792975</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>524154</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>5087513</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>351753</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3397701</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>264131</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2556361</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>26172300</v>
+        <v>25667674</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>253248160</v>
+        <v>248692213</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>12112800</v>
+        <v>11915638</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>117205760</v>
+        <v>114984833</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5515650</v>
+        <v>5393693</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>53370480</v>
+        <v>52391616</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>173580750</v>
+        <v>174336393</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>41778345</v>
+        <v>46990667</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>243170</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2472000</v>
+        <v>2432495</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2118820</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21630000</v>
+        <v>21255389</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1299797</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>13184000</v>
+        <v>12944176</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2361990</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20280519</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>206000000</v>
+        <v>201841821</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2909792</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>29870000</v>
+        <v>29224772</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14395627</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>146260000</v>
+        <v>143461789</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>525246</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>5356000</v>
+        <v>5264565</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20805765</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18443775</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4736204</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>48410000</v>
+        <v>47585064</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7560226</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>77250000</v>
+        <v>75835641</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7610709</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>77250000</v>
+        <v>75975468</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>242696</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2472000</v>
+        <v>2427480</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12539126</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6186942</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>62830000</v>
+        <v>61700398</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6154597</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>62830000</v>
+        <v>61784072</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1016380</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>10300000</v>
+        <v>10117542</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>884868</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>8961000</v>
+        <v>8808671</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>125930</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1287500</v>
+        <v>1264116</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7329252</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5209874</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>28424395</v>
+        <v>33756766</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>28424395</v>
+        <v>33756766</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
